--- a/Structure_Data/text.9.14/20260914_164/structure_factor_20260914_164.xlsx
+++ b/Structure_Data/text.9.14/20260914_164/structure_factor_20260914_164.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D391"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,4167 @@
         <v>16.873911224743</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.274051666259766</v>
+      </c>
+      <c r="C30">
+        <v>0.273117065429688</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.274051666259766</v>
+      </c>
+      <c r="C31">
+        <v>0.273117065429688</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.231437683105469</v>
+      </c>
+      <c r="C32">
+        <v>0.211334228515625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.162677764892578</v>
+      </c>
+      <c r="C33">
+        <v>0.0250930786132812</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.137439727783203</v>
+      </c>
+      <c r="C34">
+        <v>0.0181121826171875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.117652893066406</v>
+      </c>
+      <c r="C35">
+        <v>0.01031494140625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.0676193237304688</v>
+      </c>
+      <c r="C36">
+        <v>0.00180435180664062</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0485153198242188</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.037628173828125</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.0184516906738281</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0141830444335938</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.01202392578125</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0114974975585938</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.00484085083007812</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.00397872924804688</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.0031890869140625</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B46">
+        <v>0.00193023681640625</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2.5</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>17497</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>2.05295193461736</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>1.91320480705585</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.05</v>
+      </c>
+      <c r="B63">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.1</v>
+      </c>
+      <c r="B64">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.15</v>
+      </c>
+      <c r="B65">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.2</v>
+      </c>
+      <c r="B66">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.25</v>
+      </c>
+      <c r="B67">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.3</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.35</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.4</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.45</v>
+      </c>
+      <c r="B71">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.5</v>
+      </c>
+      <c r="B72">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.55</v>
+      </c>
+      <c r="B73">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.6</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.65</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.7</v>
+      </c>
+      <c r="B76">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.8</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.85</v>
+      </c>
+      <c r="B79">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.9</v>
+      </c>
+      <c r="B80">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.95</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.5</v>
+      </c>
+      <c r="B83">
+        <v>4622</v>
+      </c>
+      <c r="C83">
+        <v>0.264159570212036</v>
+      </c>
+      <c r="D83">
+        <v>0.264159570212036</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84">
+        <v>3237</v>
+      </c>
+      <c r="C84">
+        <v>0.185003143396011</v>
+      </c>
+      <c r="D84">
+        <v>0.449162713608047</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>1.5</v>
+      </c>
+      <c r="B85">
+        <v>2392</v>
+      </c>
+      <c r="C85">
+        <v>0.136709150140024</v>
+      </c>
+      <c r="D85">
+        <v>0.585871863748071</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>2</v>
+      </c>
+      <c r="B86">
+        <v>1763</v>
+      </c>
+      <c r="C86">
+        <v>0.100760130308053</v>
+      </c>
+      <c r="D86">
+        <v>0.686631994056124</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>2.5</v>
+      </c>
+      <c r="B87">
+        <v>1284</v>
+      </c>
+      <c r="C87">
+        <v>0.0733840086872035</v>
+      </c>
+      <c r="D87">
+        <v>0.760016002743327</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>971</v>
+      </c>
+      <c r="C88">
+        <v>0.0554952277533291</v>
+      </c>
+      <c r="D88">
+        <v>0.815511230496657</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>3.5</v>
+      </c>
+      <c r="B89">
+        <v>673</v>
+      </c>
+      <c r="C89">
+        <v>0.038463736640567</v>
+      </c>
+      <c r="D89">
+        <v>0.853974967137224</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90">
+        <v>555</v>
+      </c>
+      <c r="C90">
+        <v>0.0317197233811511</v>
+      </c>
+      <c r="D90">
+        <v>0.885694690518375</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>4.5</v>
+      </c>
+      <c r="B91">
+        <v>416</v>
+      </c>
+      <c r="C91">
+        <v>0.0237755043721781</v>
+      </c>
+      <c r="D91">
+        <v>0.909470194890553</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>5</v>
+      </c>
+      <c r="B92">
+        <v>352</v>
+      </c>
+      <c r="C92">
+        <v>0.0201177344687661</v>
+      </c>
+      <c r="D92">
+        <v>0.929587929359319</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>5.5</v>
+      </c>
+      <c r="B93">
+        <v>268</v>
+      </c>
+      <c r="C93">
+        <v>0.0153169114705378</v>
+      </c>
+      <c r="D93">
+        <v>0.944904840829857</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>6</v>
+      </c>
+      <c r="B94">
+        <v>219</v>
+      </c>
+      <c r="C94">
+        <v>0.012516431388238</v>
+      </c>
+      <c r="D94">
+        <v>0.957421272218094</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>6.5</v>
+      </c>
+      <c r="B95">
+        <v>176</v>
+      </c>
+      <c r="C95">
+        <v>0.010058867234383</v>
+      </c>
+      <c r="D95">
+        <v>0.967480139452478</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>7</v>
+      </c>
+      <c r="B96">
+        <v>128</v>
+      </c>
+      <c r="C96">
+        <v>0.00731553980682403</v>
+      </c>
+      <c r="D96">
+        <v>0.974795679259302</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>7.5</v>
+      </c>
+      <c r="B97">
+        <v>99</v>
+      </c>
+      <c r="C97">
+        <v>0.00565811281934046</v>
+      </c>
+      <c r="D97">
+        <v>0.980453792078642</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>8</v>
+      </c>
+      <c r="B98">
+        <v>71</v>
+      </c>
+      <c r="C98">
+        <v>0.0040578384865977</v>
+      </c>
+      <c r="D98">
+        <v>0.98451163056524</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>8.5</v>
+      </c>
+      <c r="B99">
+        <v>67</v>
+      </c>
+      <c r="C99">
+        <v>0.00382922786763445</v>
+      </c>
+      <c r="D99">
+        <v>0.988340858432874</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>9</v>
+      </c>
+      <c r="B100">
+        <v>45</v>
+      </c>
+      <c r="C100">
+        <v>0.00257186946333657</v>
+      </c>
+      <c r="D100">
+        <v>0.990912727896211</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>9.5</v>
+      </c>
+      <c r="B101">
+        <v>27</v>
+      </c>
+      <c r="C101">
+        <v>0.00154312167800194</v>
+      </c>
+      <c r="D101">
+        <v>0.992455849574213</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>10</v>
+      </c>
+      <c r="B102">
+        <v>26</v>
+      </c>
+      <c r="C102">
+        <v>0.00148596902326113</v>
+      </c>
+      <c r="D102">
+        <v>0.993941818597474</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>10.5</v>
+      </c>
+      <c r="B103">
+        <v>25</v>
+      </c>
+      <c r="C103">
+        <v>0.00142881636852032</v>
+      </c>
+      <c r="D103">
+        <v>0.995370634965994</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>11</v>
+      </c>
+      <c r="B104">
+        <v>24</v>
+      </c>
+      <c r="C104">
+        <v>0.00137166371377951</v>
+      </c>
+      <c r="D104">
+        <v>0.996742298679774</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>11.5</v>
+      </c>
+      <c r="B105">
+        <v>14</v>
+      </c>
+      <c r="C105">
+        <v>0.000800137166371378</v>
+      </c>
+      <c r="D105">
+        <v>0.997542435846145</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>12</v>
+      </c>
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106">
+        <v>0.000400068583185689</v>
+      </c>
+      <c r="D106">
+        <v>0.997942504429331</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>12.5</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+      <c r="C107">
+        <v>0.000285763273704064</v>
+      </c>
+      <c r="D107">
+        <v>0.998228267703035</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>13</v>
+      </c>
+      <c r="B108">
+        <v>6</v>
+      </c>
+      <c r="C108">
+        <v>0.000342915928444876</v>
+      </c>
+      <c r="D108">
+        <v>0.99857118363148</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>13.5</v>
+      </c>
+      <c r="B109">
+        <v>8</v>
+      </c>
+      <c r="C109">
+        <v>0.000457221237926502</v>
+      </c>
+      <c r="D109">
+        <v>0.999028404869406</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>14</v>
+      </c>
+      <c r="B110">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>0.000342915928444876</v>
+      </c>
+      <c r="D110">
+        <v>0.999371320797851</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>14.5</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D111">
+        <v>0.999428473452592</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>15</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D112">
+        <v>0.999485626107333</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>15.5</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>0.000114305309481625</v>
+      </c>
+      <c r="D113">
+        <v>0.999599931416814</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>16</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D114">
+        <v>0.999657084071555</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>17</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>0.000114305309481625</v>
+      </c>
+      <c r="D115">
+        <v>0.999771389381037</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>17.5</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D116">
+        <v>0.999828542035778</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>19</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D117">
+        <v>0.999885694690518</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>20.5</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D118">
+        <v>0.999942847345259</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>27</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>5.71526547408127e-05</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>190303</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>0.910406712703481</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.445480565134352</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.05</v>
+      </c>
+      <c r="B134">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.1</v>
+      </c>
+      <c r="B135">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>0.15</v>
+      </c>
+      <c r="B136">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.2</v>
+      </c>
+      <c r="B137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.25</v>
+      </c>
+      <c r="B138">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.3</v>
+      </c>
+      <c r="B139">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>0.35</v>
+      </c>
+      <c r="B140">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>0.4</v>
+      </c>
+      <c r="B141">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>0.45</v>
+      </c>
+      <c r="B142">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>0.5</v>
+      </c>
+      <c r="B143">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>0.55</v>
+      </c>
+      <c r="B144">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>0.6</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0.65</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>0.7</v>
+      </c>
+      <c r="B147">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>0.75</v>
+      </c>
+      <c r="B148">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>0.8</v>
+      </c>
+      <c r="B149">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>0.85</v>
+      </c>
+      <c r="B150">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>0.9</v>
+      </c>
+      <c r="B151">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>0.95</v>
+      </c>
+      <c r="B152">
+        <v>1.6583123951777</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.5</v>
+      </c>
+      <c r="B154">
+        <v>60790</v>
+      </c>
+      <c r="C154">
+        <v>0.319437948955087</v>
+      </c>
+      <c r="D154">
+        <v>0.319437948955087</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B155">
+        <v>35712</v>
+      </c>
+      <c r="C155">
+        <v>0.187658628608062</v>
+      </c>
+      <c r="D155">
+        <v>0.507096577563149</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B156">
+        <v>15538</v>
+      </c>
+      <c r="C156">
+        <v>0.0816487391160413</v>
+      </c>
+      <c r="D156">
+        <v>0.588745316679191</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>1</v>
+      </c>
+      <c r="B157">
+        <v>12999</v>
+      </c>
+      <c r="C157">
+        <v>0.0683068580106462</v>
+      </c>
+      <c r="D157">
+        <v>0.657052174689837</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B158">
+        <v>24450</v>
+      </c>
+      <c r="C158">
+        <v>0.128479319821548</v>
+      </c>
+      <c r="D158">
+        <v>0.785531494511384</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B159">
+        <v>10923</v>
+      </c>
+      <c r="C159">
+        <v>0.057397939076105</v>
+      </c>
+      <c r="D159">
+        <v>0.842929433587489</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B160">
+        <v>8379</v>
+      </c>
+      <c r="C160">
+        <v>0.0440297840811758</v>
+      </c>
+      <c r="D160">
+        <v>0.886959217668665</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>1.5</v>
+      </c>
+      <c r="B161">
+        <v>8455</v>
+      </c>
+      <c r="C161">
+        <v>0.0444291472020935</v>
+      </c>
+      <c r="D161">
+        <v>0.931388364870759</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B162">
+        <v>3225</v>
+      </c>
+      <c r="C162">
+        <v>0.016946658749468</v>
+      </c>
+      <c r="D162">
+        <v>0.948335023620227</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B163">
+        <v>2222</v>
+      </c>
+      <c r="C163">
+        <v>0.0116761165089357</v>
+      </c>
+      <c r="D163">
+        <v>0.960011140129162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B164">
+        <v>657</v>
+      </c>
+      <c r="C164">
+        <v>0.00345238908477533</v>
+      </c>
+      <c r="D164">
+        <v>0.963463529213938</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B165">
+        <v>1521</v>
+      </c>
+      <c r="C165">
+        <v>0.0079925171962607</v>
+      </c>
+      <c r="D165">
+        <v>0.971456046410198</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B166">
+        <v>1173</v>
+      </c>
+      <c r="C166">
+        <v>0.0061638544846902</v>
+      </c>
+      <c r="D166">
+        <v>0.977619900894889</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>2</v>
+      </c>
+      <c r="B167">
+        <v>178</v>
+      </c>
+      <c r="C167">
+        <v>0.000935350467412495</v>
+      </c>
+      <c r="D167">
+        <v>0.978555251362301</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B168">
+        <v>672</v>
+      </c>
+      <c r="C168">
+        <v>0.00353121075337751</v>
+      </c>
+      <c r="D168">
+        <v>0.982086462115679</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B169">
+        <v>345</v>
+      </c>
+      <c r="C169">
+        <v>0.00181289837785006</v>
+      </c>
+      <c r="D169">
+        <v>0.983899360493529</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B170">
+        <v>186</v>
+      </c>
+      <c r="C170">
+        <v>0.000977388690666989</v>
+      </c>
+      <c r="D170">
+        <v>0.984876749184196</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B171">
+        <v>175</v>
+      </c>
+      <c r="C171">
+        <v>0.000919586133692059</v>
+      </c>
+      <c r="D171">
+        <v>0.985796335317888</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B172">
+        <v>304</v>
+      </c>
+      <c r="C172">
+        <v>0.00159745248367078</v>
+      </c>
+      <c r="D172">
+        <v>0.987393787801559</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B173">
+        <v>112</v>
+      </c>
+      <c r="C173">
+        <v>0.000588535125562918</v>
+      </c>
+      <c r="D173">
+        <v>0.987982322927122</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B174">
+        <v>131</v>
+      </c>
+      <c r="C174">
+        <v>0.000688375905792342</v>
+      </c>
+      <c r="D174">
+        <v>0.988670698832914</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2.5</v>
+      </c>
+      <c r="B175">
+        <v>146</v>
+      </c>
+      <c r="C175">
+        <v>0.000767197574394518</v>
+      </c>
+      <c r="D175">
+        <v>0.989437896407308</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B176">
+        <v>297</v>
+      </c>
+      <c r="C176">
+        <v>0.0015606690383231</v>
+      </c>
+      <c r="D176">
+        <v>0.990998565445631</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B177">
+        <v>102</v>
+      </c>
+      <c r="C177">
+        <v>0.0005359873464948</v>
+      </c>
+      <c r="D177">
+        <v>0.991534552792126</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B178">
+        <v>212</v>
+      </c>
+      <c r="C178">
+        <v>0.00111401291624409</v>
+      </c>
+      <c r="D178">
+        <v>0.99264856570837</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B179">
+        <v>115</v>
+      </c>
+      <c r="C179">
+        <v>0.000604299459283353</v>
+      </c>
+      <c r="D179">
+        <v>0.993252865167654</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B180">
+        <v>27</v>
+      </c>
+      <c r="C180">
+        <v>0.000141879003483918</v>
+      </c>
+      <c r="D180">
+        <v>0.993394744171138</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B181">
+        <v>123</v>
+      </c>
+      <c r="C181">
+        <v>0.000646337682537848</v>
+      </c>
+      <c r="D181">
+        <v>0.994041081853675</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B182">
+        <v>99</v>
+      </c>
+      <c r="C182">
+        <v>0.000520223012774365</v>
+      </c>
+      <c r="D182">
+        <v>0.99456130486645</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B183">
+        <v>88</v>
+      </c>
+      <c r="C183">
+        <v>0.000462420455799436</v>
+      </c>
+      <c r="D183">
+        <v>0.995023725322249</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>3</v>
+      </c>
+      <c r="B184">
+        <v>52</v>
+      </c>
+      <c r="C184">
+        <v>0.000273248451154212</v>
+      </c>
+      <c r="D184">
+        <v>0.995296973773403</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B185">
+        <v>38</v>
+      </c>
+      <c r="C185">
+        <v>0.000199681560458847</v>
+      </c>
+      <c r="D185">
+        <v>0.995496655333862</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B186">
+        <v>106</v>
+      </c>
+      <c r="C186">
+        <v>0.000557006458122047</v>
+      </c>
+      <c r="D186">
+        <v>0.996053661791984</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B187">
+        <v>31</v>
+      </c>
+      <c r="C187">
+        <v>0.000162898115111165</v>
+      </c>
+      <c r="D187">
+        <v>0.996216559907096</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B188">
+        <v>120</v>
+      </c>
+      <c r="C188">
+        <v>0.000630573348817412</v>
+      </c>
+      <c r="D188">
+        <v>0.996847133255913</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B189">
+        <v>47</v>
+      </c>
+      <c r="C189">
+        <v>0.000246974561620153</v>
+      </c>
+      <c r="D189">
+        <v>0.997094107817533</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B190">
+        <v>31</v>
+      </c>
+      <c r="C190">
+        <v>0.000162898115111165</v>
+      </c>
+      <c r="D190">
+        <v>0.997257005932644</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B191">
+        <v>19</v>
+      </c>
+      <c r="C191">
+        <v>9.98407802294236e-05</v>
+      </c>
+      <c r="D191">
+        <v>0.997356846712874</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B192">
+        <v>65</v>
+      </c>
+      <c r="C192">
+        <v>0.000341560563942765</v>
+      </c>
+      <c r="D192">
+        <v>0.997698407276816</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B193">
+        <v>33</v>
+      </c>
+      <c r="C193">
+        <v>0.000173407670924788</v>
+      </c>
+      <c r="D193">
+        <v>0.997871814947741</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B194">
+        <v>11</v>
+      </c>
+      <c r="C194">
+        <v>5.78025569749295e-05</v>
+      </c>
+      <c r="D194">
+        <v>0.997929617504716</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>3.5</v>
+      </c>
+      <c r="B195">
+        <v>41</v>
+      </c>
+      <c r="C195">
+        <v>0.000215445894179283</v>
+      </c>
+      <c r="D195">
+        <v>0.998145063398895</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B196">
+        <v>63</v>
+      </c>
+      <c r="C196">
+        <v>0.000331051008129141</v>
+      </c>
+      <c r="D196">
+        <v>0.998476114407025</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B197">
+        <v>25</v>
+      </c>
+      <c r="C197">
+        <v>0.000131369447670294</v>
+      </c>
+      <c r="D197">
+        <v>0.998607483854695</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B198">
+        <v>11</v>
+      </c>
+      <c r="C198">
+        <v>5.78025569749295e-05</v>
+      </c>
+      <c r="D198">
+        <v>0.99866528641167</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B199">
+        <v>31</v>
+      </c>
+      <c r="C199">
+        <v>0.000162898115111165</v>
+      </c>
+      <c r="D199">
+        <v>0.998828184526781</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B200">
+        <v>41</v>
+      </c>
+      <c r="C200">
+        <v>0.000215445894179283</v>
+      </c>
+      <c r="D200">
+        <v>0.99904363042096</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B201">
+        <v>17</v>
+      </c>
+      <c r="C201">
+        <v>8.93312244158001e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.999132961645376</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B202">
+        <v>24</v>
+      </c>
+      <c r="C202">
+        <v>0.000126114669763482</v>
+      </c>
+      <c r="D202">
+        <v>0.99925907631514</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B203">
+        <v>8</v>
+      </c>
+      <c r="C203">
+        <v>4.20382232544941e-05</v>
+      </c>
+      <c r="D203">
+        <v>0.999301114538394</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B204">
+        <v>27</v>
+      </c>
+      <c r="C204">
+        <v>0.000141879003483918</v>
+      </c>
+      <c r="D204">
+        <v>0.999442993541878</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B205">
+        <v>18</v>
+      </c>
+      <c r="C205">
+        <v>9.45860023226118e-05</v>
+      </c>
+      <c r="D205">
+        <v>0.999537579544201</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B206">
+        <v>18</v>
+      </c>
+      <c r="C206">
+        <v>9.45860023226118e-05</v>
+      </c>
+      <c r="D206">
+        <v>0.999632165546523</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>4</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>5.25477790681177e-06</v>
+      </c>
+      <c r="D207">
+        <v>0.99963742032443</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B208">
+        <v>16</v>
+      </c>
+      <c r="C208">
+        <v>8.40764465089883e-05</v>
+      </c>
+      <c r="D208">
+        <v>0.999721496770939</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B209">
+        <v>13</v>
+      </c>
+      <c r="C209">
+        <v>6.8312112788553e-05</v>
+      </c>
+      <c r="D209">
+        <v>0.999789808883727</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B210">
+        <v>2</v>
+      </c>
+      <c r="C210">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D210">
+        <v>0.999800318439541</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B211">
+        <v>6</v>
+      </c>
+      <c r="C211">
+        <v>3.15286674408706e-05</v>
+      </c>
+      <c r="D211">
+        <v>0.999831847106982</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B212">
+        <v>8</v>
+      </c>
+      <c r="C212">
+        <v>4.20382232544941e-05</v>
+      </c>
+      <c r="D212">
+        <v>0.999873885330236</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B213">
+        <v>6</v>
+      </c>
+      <c r="C213">
+        <v>3.15286674408706e-05</v>
+      </c>
+      <c r="D213">
+        <v>0.999905413997677</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B214">
+        <v>2</v>
+      </c>
+      <c r="C214">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D214">
+        <v>0.999915923553491</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B215">
+        <v>2</v>
+      </c>
+      <c r="C215">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D215">
+        <v>0.999926433109305</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B216">
+        <v>6</v>
+      </c>
+      <c r="C216">
+        <v>3.15286674408706e-05</v>
+      </c>
+      <c r="D216">
+        <v>0.999957961776745</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>4.33012701892219</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217">
+        <v>5.25477790681177e-06</v>
+      </c>
+      <c r="D217">
+        <v>0.999963216554652</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>4.35889894354067</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218">
+        <v>5.25477790681177e-06</v>
+      </c>
+      <c r="D218">
+        <v>0.999968471332559</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B219">
+        <v>2</v>
+      </c>
+      <c r="C219">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D219">
+        <v>0.999978980888373</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>4.5</v>
+      </c>
+      <c r="B220">
+        <v>2</v>
+      </c>
+      <c r="C220">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D220">
+        <v>0.999989490444186</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>4.55521678957215</v>
+      </c>
+      <c r="B221">
+        <v>2</v>
+      </c>
+      <c r="C221">
+        <v>1.05095558136235e-05</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222"/>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B227">
+        <v>0.274051666259766</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B228">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>0</v>
+      </c>
+      <c r="B233">
+        <v>0.274051666259766</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>0.5</v>
+      </c>
+      <c r="B234">
+        <v>0.205984751383464</v>
+      </c>
+      <c r="C234">
+        <v>6</v>
+      </c>
+      <c r="D234">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>1</v>
+      </c>
+      <c r="B235">
+        <v>0.173361558180589</v>
+      </c>
+      <c r="C235">
+        <v>26</v>
+      </c>
+      <c r="D235">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>1.5</v>
+      </c>
+      <c r="B236">
+        <v>0.13612560696072</v>
+      </c>
+      <c r="C236">
+        <v>90</v>
+      </c>
+      <c r="D236">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>2</v>
+      </c>
+      <c r="B237">
+        <v>0.111799553259095</v>
+      </c>
+      <c r="C237">
+        <v>134</v>
+      </c>
+      <c r="D237">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>2.5</v>
+      </c>
+      <c r="B238">
+        <v>0.0947920333507449</v>
+      </c>
+      <c r="C238">
+        <v>258</v>
+      </c>
+      <c r="D238">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>3</v>
+      </c>
+      <c r="B239">
+        <v>0.0844241444657489</v>
+      </c>
+      <c r="C239">
+        <v>410</v>
+      </c>
+      <c r="D239">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>3.5</v>
+      </c>
+      <c r="B240">
+        <v>0.0804028067028957</v>
+      </c>
+      <c r="C240">
+        <v>494</v>
+      </c>
+      <c r="D240">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>4</v>
+      </c>
+      <c r="B241">
+        <v>0.0802359207816746</v>
+      </c>
+      <c r="C241">
+        <v>690</v>
+      </c>
+      <c r="D241">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>4.5</v>
+      </c>
+      <c r="B242">
+        <v>0.0812559226942162</v>
+      </c>
+      <c r="C242">
+        <v>962</v>
+      </c>
+      <c r="D242">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>5</v>
+      </c>
+      <c r="B243">
+        <v>0.0815381326310622</v>
+      </c>
+      <c r="C243">
+        <v>1098</v>
+      </c>
+      <c r="D243">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>5.5</v>
+      </c>
+      <c r="B244">
+        <v>0.0810232311699163</v>
+      </c>
+      <c r="C244">
+        <v>1406</v>
+      </c>
+      <c r="D244">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>6</v>
+      </c>
+      <c r="B245">
+        <v>0.0801212760432138</v>
+      </c>
+      <c r="C245">
+        <v>1578</v>
+      </c>
+      <c r="D245">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>6.5</v>
+      </c>
+      <c r="B246">
+        <v>0.0794031844502989</v>
+      </c>
+      <c r="C246">
+        <v>2018</v>
+      </c>
+      <c r="D246">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>7</v>
+      </c>
+      <c r="B247">
+        <v>0.0787664294548263</v>
+      </c>
+      <c r="C247">
+        <v>2342</v>
+      </c>
+      <c r="D247">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>7.5</v>
+      </c>
+      <c r="B248">
+        <v>0.0783888252739121</v>
+      </c>
+      <c r="C248">
+        <v>2634</v>
+      </c>
+      <c r="D248">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>8</v>
+      </c>
+      <c r="B249">
+        <v>0.0781004323080538</v>
+      </c>
+      <c r="C249">
+        <v>2930</v>
+      </c>
+      <c r="D249">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>8.5</v>
+      </c>
+      <c r="B250">
+        <v>0.0778210374763753</v>
+      </c>
+      <c r="C250">
+        <v>3402</v>
+      </c>
+      <c r="D250">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>9</v>
+      </c>
+      <c r="B251">
+        <v>0.077538918307164</v>
+      </c>
+      <c r="C251">
+        <v>3926</v>
+      </c>
+      <c r="D251">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>9.5</v>
+      </c>
+      <c r="B252">
+        <v>0.077164411656576</v>
+      </c>
+      <c r="C252">
+        <v>4266</v>
+      </c>
+      <c r="D252">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>10</v>
+      </c>
+      <c r="B253">
+        <v>0.0768161088165219</v>
+      </c>
+      <c r="C253">
+        <v>4730</v>
+      </c>
+      <c r="D253">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>10.5</v>
+      </c>
+      <c r="B254">
+        <v>0.0763974973813592</v>
+      </c>
+      <c r="C254">
+        <v>5510</v>
+      </c>
+      <c r="D254">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>11</v>
+      </c>
+      <c r="B255">
+        <v>0.0760128798994046</v>
+      </c>
+      <c r="C255">
+        <v>5562</v>
+      </c>
+      <c r="D255">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>11.5</v>
+      </c>
+      <c r="B256">
+        <v>0.0756888129223899</v>
+      </c>
+      <c r="C256">
+        <v>6410</v>
+      </c>
+      <c r="D256">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>12</v>
+      </c>
+      <c r="B257">
+        <v>0.0753070354323336</v>
+      </c>
+      <c r="C257">
+        <v>6894</v>
+      </c>
+      <c r="D257">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>12.5</v>
+      </c>
+      <c r="B258">
+        <v>0.0750068623806351</v>
+      </c>
+      <c r="C258">
+        <v>7490</v>
+      </c>
+      <c r="D258">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>13</v>
+      </c>
+      <c r="B259">
+        <v>0.0747517599381613</v>
+      </c>
+      <c r="C259">
+        <v>8258</v>
+      </c>
+      <c r="D259">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>13.5</v>
+      </c>
+      <c r="B260">
+        <v>0.0745793088743733</v>
+      </c>
+      <c r="C260">
+        <v>8994</v>
+      </c>
+      <c r="D260">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>14</v>
+      </c>
+      <c r="B261">
+        <v>0.0744650859134116</v>
+      </c>
+      <c r="C261">
+        <v>9446</v>
+      </c>
+      <c r="D261">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>14.5</v>
+      </c>
+      <c r="B262">
+        <v>0.0743979000811062</v>
+      </c>
+      <c r="C262">
+        <v>9978</v>
+      </c>
+      <c r="D262">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>15</v>
+      </c>
+      <c r="B263">
+        <v>0.0743590505788005</v>
+      </c>
+      <c r="C263">
+        <v>11138</v>
+      </c>
+      <c r="D263">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>15.5</v>
+      </c>
+      <c r="B264">
+        <v>0.0742919710504785</v>
+      </c>
+      <c r="C264">
+        <v>11406</v>
+      </c>
+      <c r="D264">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>16</v>
+      </c>
+      <c r="B265">
+        <v>0.0742146401376895</v>
+      </c>
+      <c r="C265">
+        <v>12575</v>
+      </c>
+      <c r="D265">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>16.5</v>
+      </c>
+      <c r="B266">
+        <v>0.0741034426991996</v>
+      </c>
+      <c r="C266">
+        <v>12848</v>
+      </c>
+      <c r="D266">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>17</v>
+      </c>
+      <c r="B267">
+        <v>0.0740522900228674</v>
+      </c>
+      <c r="C267">
+        <v>12060</v>
+      </c>
+      <c r="D267">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>17.5</v>
+      </c>
+      <c r="B268">
+        <v>0.0741243927974048</v>
+      </c>
+      <c r="C268">
+        <v>11804</v>
+      </c>
+      <c r="D268">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>18</v>
+      </c>
+      <c r="B269">
+        <v>0.07423817531389</v>
+      </c>
+      <c r="C269">
+        <v>11016</v>
+      </c>
+      <c r="D269">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>18.5</v>
+      </c>
+      <c r="B270">
+        <v>0.074346881759501</v>
+      </c>
+      <c r="C270">
+        <v>10700</v>
+      </c>
+      <c r="D270">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>19</v>
+      </c>
+      <c r="B271">
+        <v>0.074395136346383</v>
+      </c>
+      <c r="C271">
+        <v>9756</v>
+      </c>
+      <c r="D271">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>19.5</v>
+      </c>
+      <c r="B272">
+        <v>0.0743820938150054</v>
+      </c>
+      <c r="C272">
+        <v>9224</v>
+      </c>
+      <c r="D272">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>20</v>
+      </c>
+      <c r="B273">
+        <v>0.0742858120875626</v>
+      </c>
+      <c r="C273">
+        <v>8408</v>
+      </c>
+      <c r="D273">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>20.5</v>
+      </c>
+      <c r="B274">
+        <v>0.074249800980507</v>
+      </c>
+      <c r="C274">
+        <v>7452</v>
+      </c>
+      <c r="D274">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>21</v>
+      </c>
+      <c r="B275">
+        <v>0.0741804979064248</v>
+      </c>
+      <c r="C275">
+        <v>7040</v>
+      </c>
+      <c r="D275">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>21.5</v>
+      </c>
+      <c r="B276">
+        <v>0.0741953230395759</v>
+      </c>
+      <c r="C276">
+        <v>5820</v>
+      </c>
+      <c r="D276">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>22</v>
+      </c>
+      <c r="B277">
+        <v>0.0743019213441942</v>
+      </c>
+      <c r="C277">
+        <v>4880</v>
+      </c>
+      <c r="D277">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>22.5</v>
+      </c>
+      <c r="B278">
+        <v>0.0745628015781806</v>
+      </c>
+      <c r="C278">
+        <v>3936</v>
+      </c>
+      <c r="D278">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>23</v>
+      </c>
+      <c r="B279">
+        <v>0.0748168904608828</v>
+      </c>
+      <c r="C279">
+        <v>2999</v>
+      </c>
+      <c r="D279">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>23.5</v>
+      </c>
+      <c r="B280">
+        <v>0.0750739316327856</v>
+      </c>
+      <c r="C280">
+        <v>2180</v>
+      </c>
+      <c r="D280">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>24</v>
+      </c>
+      <c r="B281">
+        <v>0.0753294815251857</v>
+      </c>
+      <c r="C281">
+        <v>1620</v>
+      </c>
+      <c r="D281">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>24.5</v>
+      </c>
+      <c r="B282">
+        <v>0.0757119955606018</v>
+      </c>
+      <c r="C282">
+        <v>1208</v>
+      </c>
+      <c r="D282">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>25</v>
+      </c>
+      <c r="B283">
+        <v>0.0762758599218543</v>
+      </c>
+      <c r="C283">
+        <v>942</v>
+      </c>
+      <c r="D283">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>25.5</v>
+      </c>
+      <c r="B284">
+        <v>0.0767373646775337</v>
+      </c>
+      <c r="C284">
+        <v>584</v>
+      </c>
+      <c r="D284">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>26</v>
+      </c>
+      <c r="B285">
+        <v>0.0771641529781718</v>
+      </c>
+      <c r="C285">
+        <v>284</v>
+      </c>
+      <c r="D285">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>26.5</v>
+      </c>
+      <c r="B286">
+        <v>0.0774828990300496</v>
+      </c>
+      <c r="C286">
+        <v>192</v>
+      </c>
+      <c r="D286">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>27</v>
+      </c>
+      <c r="B287">
+        <v>0.0784023725069486</v>
+      </c>
+      <c r="C287">
+        <v>104</v>
+      </c>
+      <c r="D287">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>27.5</v>
+      </c>
+      <c r="B288">
+        <v>0.079257329305013</v>
+      </c>
+      <c r="C288">
+        <v>24</v>
+      </c>
+      <c r="D288">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>28</v>
+      </c>
+      <c r="B289">
+        <v>0.0796737670898438</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+      <c r="D289">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>0</v>
+      </c>
+      <c r="B291">
+        <v>0.274051666259766</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>0.5</v>
+      </c>
+      <c r="B292">
+        <v>0.207305908203125</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>1</v>
+      </c>
+      <c r="B293">
+        <v>0.160259246826172</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>1.5</v>
+      </c>
+      <c r="B294">
+        <v>0.127155303955078</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>2</v>
+      </c>
+      <c r="B295">
+        <v>0.104804992675781</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>2.5</v>
+      </c>
+      <c r="B296">
+        <v>0.0909652709960938</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>3</v>
+      </c>
+      <c r="B297">
+        <v>0.0832977294921875</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>3.5</v>
+      </c>
+      <c r="B298">
+        <v>0.0808906555175781</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>4</v>
+      </c>
+      <c r="B299">
+        <v>0.081512451171875</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>4.5</v>
+      </c>
+      <c r="B300">
+        <v>0.081756591796875</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>5</v>
+      </c>
+      <c r="B301">
+        <v>0.08160400390625</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>5.5</v>
+      </c>
+      <c r="B302">
+        <v>0.08074951171875</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>6</v>
+      </c>
+      <c r="B303">
+        <v>0.0793800354003906</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>6.5</v>
+      </c>
+      <c r="B304">
+        <v>0.0784492492675781</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>7</v>
+      </c>
+      <c r="B305">
+        <v>0.0777130126953125</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>7.5</v>
+      </c>
+      <c r="B306">
+        <v>0.0770149230957031</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>8</v>
+      </c>
+      <c r="B307">
+        <v>0.0767059326171875</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>8.5</v>
+      </c>
+      <c r="B308">
+        <v>0.07647705078125</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>9</v>
+      </c>
+      <c r="B309">
+        <v>0.0759201049804688</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>9.5</v>
+      </c>
+      <c r="B310">
+        <v>0.0756263732910156</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>10</v>
+      </c>
+      <c r="B311">
+        <v>0.0747222900390625</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>10.5</v>
+      </c>
+      <c r="B312">
+        <v>0.0745201110839844</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>11</v>
+      </c>
+      <c r="B313">
+        <v>0.074493408203125</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>11.5</v>
+      </c>
+      <c r="B314">
+        <v>0.0745468139648438</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>12</v>
+      </c>
+      <c r="B315">
+        <v>0.0747222900390625</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>12.5</v>
+      </c>
+      <c r="B316">
+        <v>0.0748558044433594</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>13</v>
+      </c>
+      <c r="B317">
+        <v>0.074859619140625</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>13.5</v>
+      </c>
+      <c r="B318">
+        <v>0.075164794921875</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>14</v>
+      </c>
+      <c r="B319">
+        <v>0.0753746032714844</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>14.5</v>
+      </c>
+      <c r="B320">
+        <v>0.0755119323730469</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>15</v>
+      </c>
+      <c r="B321">
+        <v>0.0756912231445312</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>15.5</v>
+      </c>
+      <c r="B322">
+        <v>0.075714111328125</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>16</v>
+      </c>
+      <c r="B323">
+        <v>0.075958251953125</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>0</v>
+      </c>
+      <c r="B325">
+        <v>0.274051666259766</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>0.5</v>
+      </c>
+      <c r="B326">
+        <v>0.20281982421875</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>1</v>
+      </c>
+      <c r="B327">
+        <v>0.153385162353516</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>1.5</v>
+      </c>
+      <c r="B328">
+        <v>0.120380401611328</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>2</v>
+      </c>
+      <c r="B329">
+        <v>0.0992965698242188</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>2.5</v>
+      </c>
+      <c r="B330">
+        <v>0.0876388549804688</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>3</v>
+      </c>
+      <c r="B331">
+        <v>0.0828323364257812</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>3.5</v>
+      </c>
+      <c r="B332">
+        <v>0.0818977355957031</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>4</v>
+      </c>
+      <c r="B333">
+        <v>0.0840415954589844</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>4.5</v>
+      </c>
+      <c r="B334">
+        <v>0.0837554931640625</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>5</v>
+      </c>
+      <c r="B335">
+        <v>0.0826873779296875</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>5.5</v>
+      </c>
+      <c r="B336">
+        <v>0.0813674926757812</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>6</v>
+      </c>
+      <c r="B337">
+        <v>0.0803146362304688</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>6.5</v>
+      </c>
+      <c r="B338">
+        <v>0.0791854858398438</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>7</v>
+      </c>
+      <c r="B339">
+        <v>0.077972412109375</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>7.5</v>
+      </c>
+      <c r="B340">
+        <v>0.077056884765625</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>8</v>
+      </c>
+      <c r="B341">
+        <v>0.0764503479003906</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>8.5</v>
+      </c>
+      <c r="B342">
+        <v>0.0765457153320312</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>9</v>
+      </c>
+      <c r="B343">
+        <v>0.0770111083984375</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>9.5</v>
+      </c>
+      <c r="B344">
+        <v>0.0778999328613281</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>10</v>
+      </c>
+      <c r="B345">
+        <v>0.0789260864257812</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>10.5</v>
+      </c>
+      <c r="B346">
+        <v>0.0797271728515625</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>11</v>
+      </c>
+      <c r="B347">
+        <v>0.080108642578125</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>11.5</v>
+      </c>
+      <c r="B348">
+        <v>0.07879638671875</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>12</v>
+      </c>
+      <c r="B349">
+        <v>0.077056884765625</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>12.5</v>
+      </c>
+      <c r="B350">
+        <v>0.0752334594726562</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>13</v>
+      </c>
+      <c r="B351">
+        <v>0.0739517211914062</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>13.5</v>
+      </c>
+      <c r="B352">
+        <v>0.0727691650390625</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>14</v>
+      </c>
+      <c r="B353">
+        <v>0.0719108581542969</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>14.5</v>
+      </c>
+      <c r="B354">
+        <v>0.0721168518066406</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>15</v>
+      </c>
+      <c r="B355">
+        <v>0.0726394653320312</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>15.5</v>
+      </c>
+      <c r="B356">
+        <v>0.0731010437011719</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>16</v>
+      </c>
+      <c r="B357">
+        <v>0.0730667114257812</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>0</v>
+      </c>
+      <c r="B359">
+        <v>0.274051666259766</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>0.5</v>
+      </c>
+      <c r="B360">
+        <v>0.207828521728516</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>1</v>
+      </c>
+      <c r="B361">
+        <v>0.160308837890625</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>1.5</v>
+      </c>
+      <c r="B362">
+        <v>0.126445770263672</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>2</v>
+      </c>
+      <c r="B363">
+        <v>0.103473663330078</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>2.5</v>
+      </c>
+      <c r="B364">
+        <v>0.08856201171875</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>3</v>
+      </c>
+      <c r="B365">
+        <v>0.0805740356445312</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>3.5</v>
+      </c>
+      <c r="B366">
+        <v>0.0777091979980469</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>4</v>
+      </c>
+      <c r="B367">
+        <v>0.07867431640625</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>4.5</v>
+      </c>
+      <c r="B368">
+        <v>0.0797119140625</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>5</v>
+      </c>
+      <c r="B369">
+        <v>0.0802383422851562</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>5.5</v>
+      </c>
+      <c r="B370">
+        <v>0.079620361328125</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>6</v>
+      </c>
+      <c r="B371">
+        <v>0.0786323547363281</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>6.5</v>
+      </c>
+      <c r="B372">
+        <v>0.0782890319824219</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>7</v>
+      </c>
+      <c r="B373">
+        <v>0.078277587890625</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>7.5</v>
+      </c>
+      <c r="B374">
+        <v>0.0787124633789062</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>8</v>
+      </c>
+      <c r="B375">
+        <v>0.0787887573242188</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>8.5</v>
+      </c>
+      <c r="B376">
+        <v>0.0786590576171875</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>9</v>
+      </c>
+      <c r="B377">
+        <v>0.077728271484375</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>9.5</v>
+      </c>
+      <c r="B378">
+        <v>0.0767860412597656</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>10</v>
+      </c>
+      <c r="B379">
+        <v>0.0759811401367188</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>10.5</v>
+      </c>
+      <c r="B380">
+        <v>0.075531005859375</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>11</v>
+      </c>
+      <c r="B381">
+        <v>0.0750999450683594</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>11.5</v>
+      </c>
+      <c r="B382">
+        <v>0.0749588012695312</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>12</v>
+      </c>
+      <c r="B383">
+        <v>0.0754165649414062</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>12.5</v>
+      </c>
+      <c r="B384">
+        <v>0.0762786865234375</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>13</v>
+      </c>
+      <c r="B385">
+        <v>0.0767135620117188</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>13.5</v>
+      </c>
+      <c r="B386">
+        <v>0.0767974853515625</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>14</v>
+      </c>
+      <c r="B387">
+        <v>0.0765113830566406</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>14.5</v>
+      </c>
+      <c r="B388">
+        <v>0.0758819580078125</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>15</v>
+      </c>
+      <c r="B389">
+        <v>0.0750808715820312</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>15.5</v>
+      </c>
+      <c r="B390">
+        <v>0.0743179321289062</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>16</v>
+      </c>
+      <c r="B391">
+        <v>0.0739898681640625</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>